--- a/AAII_Financials/Yearly/AIFF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AIFF_YR_FIN.xlsx
@@ -2175,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
